--- a/outputs/54274.xlsx
+++ b/outputs/54274.xlsx
@@ -152,35 +152,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -417,7 +417,7 @@
         <v>1094</v>
       </c>
       <c r="G4" s="8" t="n">
-        <f aca="false">IF(F4&lt;=B4,F4/B4,IF(F4=C4,MIN(F4/B4,1.1),IF(F4&lt;C4,MIN(F4/B4,1.09),IF(F4&gt;=D4,MIN(F4/B4,1.2),MIN(F4/B4,1.19)))))</f>
+        <f aca="false">IF(F4&lt;=B4,F4/B4,IF(F4&lt;C4,MIN(F4/B4,1.09),IF(F4=C4,MIN(F4/B4,1.1),IF(F4&lt;D4,MIN(F4/B4,1.19),MIN(F4/B4,1.2)))))</f>
         <v>1.09</v>
       </c>
     </row>

--- a/outputs/54274.xlsx
+++ b/outputs/54274.xlsx
@@ -417,7 +417,7 @@
         <v>1094</v>
       </c>
       <c r="G4" s="8" t="n">
-        <f aca="false">IF(F4&lt;=B4,F4/B4,IF(F4&lt;C4,MIN(F4/B4,1.09),IF(F4=C4,MIN(F4/B4,1.1),IF(F4&lt;D4,MIN(F4/B4,1.19),MIN(F4/B4,1.2)))))</f>
+        <f aca="false">IF(F4&lt;=B4,F4/B4,IF(F4&lt;=C4,MIN(F4/B4,1.09),IF(F4&lt;=D4,MIN(F4/B4,1.1),IF(F4&lt;=E4,MIN(F4/B4,1.19),MIN(F4/B4,1.2)))))</f>
         <v>1.09</v>
       </c>
     </row>
